--- a/diseases/d100/1990-1994.xlsx
+++ b/diseases/d100/1990-1994.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25363,7 +25363,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">

--- a/diseases/d100/1990-1994.xlsx
+++ b/diseases/d100/1990-1994.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12503,7 +12503,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25363,7 +25363,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN126" t="b">
